--- a/exports/Kakawa_Chocolates_Enterprise_SEO_Package_v19_V18_Structure/01_Audit_Reports/GBP_Local_Audit.xlsx
+++ b/exports/Kakawa_Chocolates_Enterprise_SEO_Package_v19_V18_Structure/01_Audit_Reports/GBP_Local_Audit.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R1f6adb3b9bae4d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="2" r:id="Re70575f9a0a04d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local SEO Audit" sheetId="1" r:id="R81267c10552d480f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +20,7 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="20"/>
+      <x:sz val="18"/>
       <x:color rgb="FFFFFEFA"/>
       <x:name val="Georgia"/>
     </x:font>
@@ -32,18 +31,18 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF3E4C83"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFEFA"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color rgb="FFFFFEFA"/>
-      <x:name val="Georgia"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +61,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFEFA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF3E4C83"/>
       </x:patternFill>
     </x:fill>
@@ -71,27 +75,13 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="1">
     <x:border/>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD8D4C9"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -105,14 +95,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -132,7 +125,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Quality controls</a:t>
+              <a:t>Priority distribution</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -146,11 +139,11 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Value</c:v>
+            <c:v>Rows</c:v>
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'Overview'!$A$15:$A$17</c:f>
+              <c:f>'Local SEO Audit'!$H$6:$H$9</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -158,7 +151,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Overview'!$B$15:$B$17</c:f>
+              <c:f>'Local SEO Audit'!$I$6:$I$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="0"/>
@@ -236,15 +229,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -258,7 +251,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c7c39b0ce584459"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e98c867529e4003"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -268,13 +261,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="GBPandLocalAudit6" displayName="GBPandLocalAudit6" ref="A5:D10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:D10"/>
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="Status"/>
-    <x:tableColumn id="2" name="Source"/>
-    <x:tableColumn id="3" name="Reason"/>
-    <x:tableColumn id="4" name="As of"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="GBPandLocalAudit60" displayName="GBPandLocalAudit60" ref="A5:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:E12"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Check"/>
+    <x:tableColumn id="2" name="Current Status"/>
+    <x:tableColumn id="3" name="Issue"/>
+    <x:tableColumn id="4" name="Recommendation"/>
+    <x:tableColumn id="5" name="Priority"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -475,272 +469,220 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20.600000381469727" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="36" customHeight="1">
+    <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>GBP and Local Audit</x:v>
+        <x:v>GBP and Local Audit - Local SEO Audit</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
       <x:c r="D1" s="3"/>
       <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-    </x:row>
-    <x:row r="2" ht="34" customHeight="1">
+    </x:row>
+    <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Traffic Radius enterprise SEO evidence register ? professional V18-compatible v19 edition</x:v>
+        <x:v>Local scoring withheld until GBP/BrightLocal evidence.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
       <x:c r="D2" s="6"/>
       <x:c r="E2" s="6"/>
-      <x:c r="F2" s="6"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>Control</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>Canonical value</x:v>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Evidence as of 2026-07-15 | Domain kakawachocolates.com.au | Run KAKAWA-ENT-20260715 | UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Current Status</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Issue</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="H5" s="13" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="I5" s="13" t="str">
+        <x:v>Rows</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="10" t="str">
-        <x:v>Evidence as of</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>2026-07-15</x:v>
+      <x:c r="A6" s="9" t="str">
+        <x:v>GBP ownership</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>Connect approved GBP export.</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:f>COUNTIF(E6:E12,H6)</x:f>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="10" t="str">
-        <x:v>Approved domain</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>kakawachocolates.com.au</x:v>
+      <x:c r="A7" s="9" t="str">
+        <x:v>NAP consistency</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>Reconcile verified facts.</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:f>COUNTIF(E6:E12,H7)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="10" t="str">
-        <x:v>Run</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>KAKAWA-ENT-20260715</x:v>
+      <x:c r="A8" s="9" t="str">
+        <x:v>Categories</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>Validate from GBP.</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:f>COUNTIF(E6:E12,H8)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="10" t="str">
-        <x:v>Evidence status</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
+      <x:c r="A9" s="9" t="str">
+        <x:v>Opening hours</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
         <x:v>UNAVAILABLE</x:v>
       </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>Validate current hours.</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:f>COUNTIF(E6:E12,H9)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="10" t="str">
-        <x:v>Decision</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>Connect GBP or BrightLocal evidence before local scoring.</x:v>
+      <x:c r="A10" s="9" t="str">
+        <x:v>Reviews</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>Import official evidence.</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="str">
+        <x:v>P1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="10" t="str">
-        <x:v>Record count</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="n">
-        <x:f>MAX(0,COUNTA(Register!A6:A1000))</x:f>
-        <x:v>5</x:v>
+      <x:c r="A11" s="9" t="str">
+        <x:v>Citation consistency</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>Import BrightLocal evidence.</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="str">
+        <x:v>P2</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="10" t="str">
-        <x:v>Release class</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="str">
-        <x:f>IF(B11&gt;0,"REVIEW READY","UNAVAILABLE")</x:f>
-        <x:v>REVIEW READY</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="12" t="str">
-        <x:v>Quality gate</x:v>
-      </x:c>
-      <x:c r="B14" s="12" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C14" t="str"/>
-      <x:c r="D14" t="str"/>
-      <x:c r="E14" t="str"/>
-      <x:c r="F14" t="str"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>Evidence-linked</x:v>
-      </x:c>
-      <x:c r="B15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" t="str"/>
-      <x:c r="D15" t="str"/>
-      <x:c r="E15" t="str"/>
-      <x:c r="F15" t="str"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>Approval required</x:v>
-      </x:c>
-      <x:c r="B16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" t="str"/>
-      <x:c r="D16" t="str"/>
-      <x:c r="E16" t="str"/>
-      <x:c r="F16" t="str"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>Fabricated substitutes</x:v>
-      </x:c>
-      <x:c r="B17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" t="str"/>
-      <x:c r="D17" t="str"/>
-      <x:c r="E17" t="str"/>
-      <x:c r="F17" t="str"/>
+      <x:c r="A12" s="9" t="str">
+        <x:v>Local schema</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>UNAVAILABLE</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>Approved local source not connected</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>Require fact pack and approval.</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="str">
+        <x:v>P1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc80ddb834d640be"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="13" t="str">
-        <x:v>GBP and Local Audit</x:v>
-      </x:c>
-      <x:c r="B1" s="13"/>
-      <x:c r="C1" s="13"/>
-      <x:c r="D1" s="13"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="6" t="str">
-        <x:v>Canonical values only. Unavailable evidence is labelled explicitly; no estimates or fabricated substitutes.</x:v>
-      </x:c>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2" s="6"/>
-      <x:c r="D2" s="6"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Reason</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>As of</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>UNAVAILABLE</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>Google Search Console</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>credential_not_configured</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="n">
-        <x:v>46218.361587928244</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>UNAVAILABLE</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>Google Analytics 4</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>credential_not_configured</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="n">
-        <x:v>46218.361587928244</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>UNAVAILABLE</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>SEMrush</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>credential_not_configured</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="n">
-        <x:v>46218.361587928244</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>UNAVAILABLE</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>PageSpeed Insights</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>credential_not_configured</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="n">
-        <x:v>46218.361587928244</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>UNAVAILABLE</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>OpenAI generation</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>credential_not_configured</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="n">
-        <x:v>46218.361587928244</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a4feb85487045a8"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc423d430e646f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2139515dbf1b434e"/>
   </x:tableParts>
 </x:worksheet>
 </file>